--- a/AAII_Financials/Quarterly/WEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>WEL</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,8 +729,11 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,8 +779,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -822,8 +829,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -869,8 +879,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +901,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,8 +949,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,8 +999,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,8 +1049,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1076,8 +1099,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1092,37 +1118,38 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
         <v>700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
+      <c r="L17" s="3">
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
@@ -1139,8 +1166,11 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,28 +1178,28 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="L18" s="3">
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1186,8 +1216,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1205,8 +1238,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1214,28 +1248,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1252,8 +1286,11 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1261,11 +1298,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>500</v>
+      </c>
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,8 +1336,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1346,37 +1386,40 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="L23" s="3">
+        <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
@@ -1393,8 +1436,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1440,8 +1486,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1487,37 +1536,40 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="L26" s="3">
+        <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
@@ -1534,37 +1586,40 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
+      <c r="L27" s="3">
+        <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
@@ -1581,8 +1636,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,8 +1686,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1736,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,8 +1786,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1769,8 +1836,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1778,28 +1848,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1816,37 +1886,40 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
+      <c r="L33" s="3">
+        <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
@@ -1863,8 +1936,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1910,37 +1986,40 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
+      <c r="L35" s="3">
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
@@ -1957,43 +2036,46 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2009,8 +2091,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2028,8 +2113,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2047,8 +2133,9 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2056,26 +2143,26 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2181,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2141,8 +2231,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2188,8 +2281,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2235,37 +2331,40 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
       </c>
       <c r="H45" s="3">
         <v>500</v>
       </c>
       <c r="I45" s="3">
+        <v>500</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
+      <c r="L45" s="3">
+        <v>0</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
@@ -2282,37 +2381,40 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
         <v>100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
+      <c r="L46" s="3">
+        <v>0</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
@@ -2329,31 +2431,34 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>59100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>57800</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>121400</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>119000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>117800</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>117500</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>117300</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2376,8 +2481,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2423,8 +2531,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2470,8 +2581,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2517,8 +2631,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2564,38 +2681,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>57800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>121400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>119000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>117800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>117600</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
-        <v>117500</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>200</v>
+      </c>
+      <c r="K52" s="3">
         <v>117300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,8 +2731,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2658,38 +2781,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E54" s="3">
         <v>58000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>121800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>118800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>118700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>118800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2705,8 +2831,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2724,8 +2853,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,16 +2873,17 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -2761,17 +2892,17 @@
         <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>0</v>
       </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,20 +2921,23 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,12 +2950,12 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,22 +2971,25 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>100</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
@@ -2866,8 +3003,8 @@
       <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3">
+        <v>100</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -2884,22 +3021,25 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>100</v>
       </c>
       <c r="H60" s="3">
         <v>100</v>
@@ -2911,11 +3051,11 @@
         <v>100</v>
       </c>
       <c r="K60" s="3">
+        <v>100</v>
+      </c>
+      <c r="L60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2931,8 +3071,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2978,8 +3121,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3004,8 +3150,8 @@
       <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>4000</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -3025,8 +3171,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3072,8 +3221,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,8 +3271,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3166,38 +3321,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>4200</v>
       </c>
       <c r="H66" s="3">
         <v>4200</v>
       </c>
       <c r="I66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J66" s="3">
         <v>4100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3213,8 +3371,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3232,8 +3393,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3279,8 +3441,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3326,8 +3491,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3373,8 +3541,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3420,37 +3591,40 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2400</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
+      <c r="L72" s="3">
+        <v>0</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3641,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3514,8 +3691,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3561,8 +3741,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3608,37 +3791,40 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E76" s="3">
         <v>51200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>115600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>115500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>114700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>114600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>114700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>114900</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
+      <c r="L76" s="3">
+        <v>0</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
@@ -3655,8 +3841,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3702,43 +3891,46 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3754,37 +3946,40 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
+      <c r="L81" s="3">
+        <v>0</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
@@ -3801,8 +3996,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3820,8 +4018,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3867,8 +4066,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3914,8 +4116,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3961,8 +4166,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4008,8 +4216,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4055,8 +4266,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4102,37 +4316,40 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -4149,8 +4366,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4168,8 +4388,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4215,8 +4436,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4262,8 +4486,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4309,26 +4536,29 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>63400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4338,8 +4568,8 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -4356,8 +4586,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4375,8 +4608,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4422,8 +4656,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,8 +4706,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4516,8 +4756,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4563,37 +4806,40 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-64900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>0</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>119100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4610,8 +4856,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4657,19 +4906,22 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-300</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
@@ -4678,16 +4930,16 @@
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4702,6 +4954,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>WEL</t>
   </si>
@@ -656,70 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -732,8 +733,14 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -782,8 +789,14 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -832,8 +845,14 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,8 +901,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,8 +927,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -952,8 +979,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1002,8 +1035,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1052,8 +1091,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,8 +1147,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1119,43 +1170,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>300</v>
+      </c>
+      <c r="F17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
       </c>
       <c r="J17" s="3">
         <v>200</v>
       </c>
       <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
@@ -1169,8 +1222,14 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1178,34 +1237,34 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-300</v>
       </c>
       <c r="J18" s="3">
         <v>-200</v>
       </c>
       <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
@@ -1219,8 +1278,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1239,8 +1304,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1248,34 +1315,34 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="F20" s="3">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3">
         <v>1200</v>
       </c>
       <c r="H20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1289,8 +1356,14 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1301,14 +1374,14 @@
         <v>500</v>
       </c>
       <c r="F21" s="3">
+        <v>300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>500</v>
+      </c>
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,8 +1412,14 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1389,43 +1468,49 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>500</v>
       </c>
       <c r="F23" s="3">
+        <v>300</v>
+      </c>
+      <c r="G23" s="3">
+        <v>500</v>
+      </c>
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-200</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
       </c>
       <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
@@ -1439,8 +1524,14 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1489,8 +1580,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1539,43 +1636,49 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>500</v>
       </c>
       <c r="F26" s="3">
+        <v>300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>500</v>
+      </c>
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-200</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
       </c>
       <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
@@ -1589,43 +1692,49 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>500</v>
       </c>
       <c r="F27" s="3">
+        <v>300</v>
+      </c>
+      <c r="G27" s="3">
+        <v>500</v>
+      </c>
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-200</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
       </c>
       <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
@@ -1639,8 +1748,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1689,8 +1804,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,8 +1860,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1789,8 +1916,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1839,8 +1972,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1848,34 +1987,34 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-1200</v>
+        <v>-700</v>
       </c>
       <c r="F32" s="3">
-        <v>-1300</v>
+        <v>-800</v>
       </c>
       <c r="G32" s="3">
         <v>-1200</v>
       </c>
       <c r="H32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1889,43 +2028,49 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <v>500</v>
       </c>
       <c r="F33" s="3">
+        <v>300</v>
+      </c>
+      <c r="G33" s="3">
+        <v>500</v>
+      </c>
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-200</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
       </c>
       <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
@@ -1939,8 +2084,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1989,43 +2140,49 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <v>500</v>
       </c>
       <c r="F35" s="3">
+        <v>300</v>
+      </c>
+      <c r="G35" s="3">
+        <v>500</v>
+      </c>
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-200</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
       </c>
       <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
@@ -2039,49 +2196,55 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2257,14 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2114,8 +2283,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2134,8 +2305,10 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2146,29 +2319,29 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,8 +2357,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2234,8 +2413,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2284,8 +2469,14 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2334,8 +2525,14 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2343,34 +2540,34 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2384,8 +2581,14 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2393,34 +2596,34 @@
         <v>0</v>
       </c>
       <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3">
         <v>100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
+      <c r="N46" s="3">
+        <v>0</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
@@ -2434,38 +2637,44 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>47500</v>
+      </c>
+      <c r="F47" s="3">
         <v>59100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>57800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>121400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>119000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>117800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>117500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>117300</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2484,8 +2693,14 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2534,8 +2749,14 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2584,8 +2805,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2634,8 +2861,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2684,8 +2917,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2704,23 +2943,23 @@
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>117300</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>117300</v>
+      </c>
+      <c r="N52" s="3">
+        <v>200</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2734,8 +2973,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2784,44 +3029,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>47500</v>
+      </c>
+      <c r="F54" s="3">
         <v>59100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>58000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>121800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>119800</v>
-      </c>
-      <c r="H54" s="3">
-        <v>118800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>118700</v>
       </c>
       <c r="J54" s="3">
         <v>118800</v>
       </c>
       <c r="K54" s="3">
+        <v>118700</v>
+      </c>
+      <c r="L54" s="3">
+        <v>118800</v>
+      </c>
+      <c r="M54" s="3">
         <v>119100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,8 +3085,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2854,8 +3111,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2874,41 +3133,43 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>300</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,8 +3185,14 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2933,17 +3200,17 @@
         <v>1800</v>
       </c>
       <c r="E58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,15 +3220,15 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2974,28 +3241,34 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
@@ -3006,11 +3279,11 @@
       <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>100</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -3024,28 +3297,34 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F60" s="3">
         <v>3500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>100</v>
       </c>
       <c r="J60" s="3">
         <v>100</v>
@@ -3054,14 +3333,14 @@
         <v>100</v>
       </c>
       <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,8 +3353,14 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3124,8 +3409,14 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3153,11 +3444,11 @@
       <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M62" s="3">
+        <v>4000</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3174,8 +3465,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3224,8 +3521,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3274,8 +3577,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3324,44 +3633,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F66" s="3">
         <v>7600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J66" s="3">
-        <v>4100</v>
       </c>
       <c r="K66" s="3">
         <v>4200</v>
       </c>
       <c r="L66" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,8 +3689,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3394,8 +3715,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3444,8 +3767,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3494,8 +3823,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3544,8 +3879,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3594,43 +3935,49 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-7500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-6600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-5800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-3500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-3100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-2900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-2600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-2400</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3644,8 +3991,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3694,8 +4047,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3744,8 +4103,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3794,43 +4159,49 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>39300</v>
+      </c>
+      <c r="F76" s="3">
         <v>51500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>51200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>115600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>115500</v>
-      </c>
-      <c r="H76" s="3">
-        <v>114700</v>
-      </c>
-      <c r="I76" s="3">
-        <v>114600</v>
       </c>
       <c r="J76" s="3">
         <v>114700</v>
       </c>
       <c r="K76" s="3">
+        <v>114600</v>
+      </c>
+      <c r="L76" s="3">
+        <v>114700</v>
+      </c>
+      <c r="M76" s="3">
         <v>114900</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -3844,8 +4215,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3894,49 +4271,55 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3949,43 +4332,49 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
         <v>500</v>
       </c>
       <c r="F81" s="3">
+        <v>300</v>
+      </c>
+      <c r="G81" s="3">
+        <v>500</v>
+      </c>
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-200</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
       </c>
       <c r="L81" s="3">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N81" s="3">
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
@@ -3999,8 +4388,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4019,8 +4414,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4069,8 +4466,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4119,8 +4522,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4169,8 +4578,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4219,8 +4634,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4269,8 +4690,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4319,43 +4746,49 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>600</v>
+      </c>
+      <c r="F89" s="3">
         <v>800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4369,8 +4802,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4389,8 +4828,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4439,8 +4880,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4489,8 +4936,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4539,43 +4992,49 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>58900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>63400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>200</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4589,8 +5048,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4609,8 +5074,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4659,8 +5126,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4709,8 +5182,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4759,8 +5238,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4809,43 +5294,49 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-64900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>119100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4859,8 +5350,14 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4909,43 +5406,49 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E102" s="3">
-        <v>-100</v>
+        <v>47500</v>
       </c>
       <c r="F102" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
       </c>
       <c r="H102" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="I102" s="3">
         <v>-100</v>
       </c>
       <c r="J102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -4957,6 +5460,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>WEL</t>
   </si>
@@ -656,74 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -739,8 +740,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -795,8 +799,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -851,8 +858,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -907,8 +917,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,8 +942,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -985,8 +999,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1041,8 +1058,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1097,8 +1117,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1153,8 +1176,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1172,8 +1198,9 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1181,37 +1208,37 @@
         <v>600</v>
       </c>
       <c r="E17" s="3">
+        <v>600</v>
+      </c>
+      <c r="F17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
@@ -1228,8 +1255,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1237,37 +1267,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
@@ -1284,8 +1314,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1306,8 +1339,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1315,37 +1349,37 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>500</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1362,8 +1396,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1371,20 +1408,20 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1418,8 +1455,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1474,46 +1514,49 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="O23" s="3">
+        <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
@@ -1530,8 +1573,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1586,8 +1632,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1642,46 +1691,49 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="O26" s="3">
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
@@ -1698,46 +1750,49 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="O27" s="3">
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
@@ -1754,8 +1809,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1810,8 +1868,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1866,8 +1927,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1922,8 +1986,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1978,8 +2045,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1987,37 +2057,37 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -2034,46 +2104,49 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="O33" s="3">
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
@@ -2090,8 +2163,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2146,46 +2222,49 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="O35" s="3">
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
@@ -2202,52 +2281,55 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2263,8 +2345,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2285,8 +2370,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2307,8 +2393,9 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2325,26 +2412,26 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,8 +2450,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2419,31 +2509,34 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2475,8 +2568,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2531,13 +2627,16 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -2546,31 +2645,31 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
       </c>
       <c r="K45" s="3">
         <v>500</v>
       </c>
       <c r="L45" s="3">
+        <v>500</v>
+      </c>
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2587,13 +2686,16 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
@@ -2602,31 +2704,31 @@
         <v>0</v>
       </c>
       <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
         <v>100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1800</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3">
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
@@ -2643,41 +2745,44 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E47" s="3">
         <v>48500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>57800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>121400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>119000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>117800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>117500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>117300</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2699,8 +2804,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2755,8 +2863,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2811,8 +2922,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2867,8 +2981,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2923,47 +3040,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>117300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,8 +3099,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3035,47 +3158,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E54" s="3">
         <v>48500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>59100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>58000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>121800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>118800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>118800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3217,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3113,8 +3242,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3135,8 +3265,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3144,16 +3275,16 @@
         <v>400</v>
       </c>
       <c r="E57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F57" s="3">
         <v>300</v>
       </c>
       <c r="G57" s="3">
+        <v>300</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -3162,17 +3293,17 @@
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3191,13 +3322,16 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="E58" s="3">
         <v>1800</v>
@@ -3206,14 +3340,14 @@
         <v>1800</v>
       </c>
       <c r="G58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,12 +3360,12 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3247,31 +3381,34 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>2800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>100</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -3285,8 +3422,8 @@
       <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>100</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
@@ -3303,31 +3440,34 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>100</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
@@ -3339,11 +3479,11 @@
         <v>100</v>
       </c>
       <c r="N60" s="3">
+        <v>100</v>
+      </c>
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3359,8 +3499,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3415,8 +3558,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3450,8 +3596,8 @@
       <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>4000</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3471,8 +3617,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3527,8 +3676,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3583,8 +3735,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3639,47 +3794,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>4200</v>
       </c>
       <c r="K66" s="3">
         <v>4200</v>
       </c>
       <c r="L66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M66" s="3">
         <v>4100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,8 +3853,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3717,8 +3878,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3773,8 +3935,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3829,8 +3994,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3885,8 +4053,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3941,46 +4112,49 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2400</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
@@ -3997,8 +4171,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4053,8 +4230,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4109,8 +4289,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4165,46 +4348,49 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E76" s="3">
         <v>39600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>115600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>115500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>114700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>114600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>114700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>114900</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="O76" s="3">
+        <v>0</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
@@ -4221,8 +4407,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4277,52 +4466,55 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4338,46 +4530,49 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="O81" s="3">
+        <v>0</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
@@ -4394,8 +4589,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4416,8 +4614,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4472,8 +4671,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4528,8 +4730,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4584,8 +4789,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4640,8 +4848,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4696,8 +4907,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4752,8 +4966,11 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4761,37 +4978,37 @@
         <v>300</v>
       </c>
       <c r="E89" s="3">
+        <v>300</v>
+      </c>
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
@@ -4808,8 +5025,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4830,8 +5050,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4886,8 +5107,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4942,8 +5166,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4998,8 +5225,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5007,26 +5237,26 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>58900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>63400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5036,8 +5266,8 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -5054,8 +5284,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5076,8 +5309,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5132,8 +5366,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5188,8 +5425,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5244,8 +5484,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5300,46 +5543,49 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-64900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>119100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
@@ -5356,8 +5602,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5412,28 +5661,31 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>47500</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-100</v>
       </c>
       <c r="J102" s="3">
         <v>-100</v>
@@ -5442,16 +5694,16 @@
         <v>-100</v>
       </c>
       <c r="L102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
@@ -5466,6 +5718,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
